--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/36.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/36.xlsx
@@ -426,13 +426,13 @@
         <v>-15.08416019179033</v>
       </c>
       <c r="E2">
-        <v>-28.65682411208071</v>
+        <v>-31.06940939593316</v>
       </c>
       <c r="F2">
-        <v>-3.171050248395989</v>
+        <v>-3.587778704455148</v>
       </c>
       <c r="G2">
-        <v>-19.62746422753317</v>
+        <v>-24.94270896283725</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.9603214492054</v>
       </c>
       <c r="E3">
-        <v>-29.70999319814857</v>
+        <v>-31.50596108298359</v>
       </c>
       <c r="F3">
-        <v>-2.650509077726816</v>
+        <v>-3.991653011451642</v>
       </c>
       <c r="G3">
-        <v>-20.76743403125351</v>
+        <v>-24.69261876589132</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.76497058607721</v>
       </c>
       <c r="E4">
-        <v>-29.81910904360039</v>
+        <v>-32.47149740429202</v>
       </c>
       <c r="F4">
-        <v>-2.91868750262367</v>
+        <v>-3.904804954607816</v>
       </c>
       <c r="G4">
-        <v>-20.00220970621482</v>
+        <v>-23.86875805826107</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.49790713683769</v>
       </c>
       <c r="E5">
-        <v>-29.12866393283591</v>
+        <v>-32.21857760248962</v>
       </c>
       <c r="F5">
-        <v>-3.084410448880043</v>
+        <v>-3.948607884669998</v>
       </c>
       <c r="G5">
-        <v>-19.57346426396935</v>
+        <v>-23.3049109078307</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.16669576469628</v>
       </c>
       <c r="E6">
-        <v>-29.22475815127867</v>
+        <v>-34.83542197069505</v>
       </c>
       <c r="F6">
-        <v>-2.353703584702478</v>
+        <v>-3.434897237614116</v>
       </c>
       <c r="G6">
-        <v>-19.32033333094559</v>
+        <v>-25.4338085303149</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.75352191911433</v>
       </c>
       <c r="E7">
-        <v>-30.70477440459853</v>
+        <v>-33.97618931247968</v>
       </c>
       <c r="F7">
-        <v>-2.672913765312538</v>
+        <v>-3.203484545544188</v>
       </c>
       <c r="G7">
-        <v>-20.12770421124474</v>
+        <v>-23.68294210296008</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.26570035364143</v>
       </c>
       <c r="E8">
-        <v>-31.07853653529562</v>
+        <v>-34.6268698929828</v>
       </c>
       <c r="F8">
-        <v>-2.765136920033366</v>
+        <v>-2.963892804273974</v>
       </c>
       <c r="G8">
-        <v>-19.93243830370191</v>
+        <v>-23.92035622103614</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.70157361039233</v>
       </c>
       <c r="E9">
-        <v>-31.06841766012548</v>
+        <v>-35.54022234406385</v>
       </c>
       <c r="F9">
-        <v>-2.386114918114905</v>
+        <v>-2.679826641633431</v>
       </c>
       <c r="G9">
-        <v>-19.25803714026036</v>
+        <v>-22.93190677610271</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.04555248420777</v>
       </c>
       <c r="E10">
-        <v>-32.24338458310364</v>
+        <v>-35.29262349922046</v>
       </c>
       <c r="F10">
-        <v>-2.707737082834178</v>
+        <v>-3.178245816222788</v>
       </c>
       <c r="G10">
-        <v>-18.4857299030404</v>
+        <v>-23.82812938813036</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.31344104563891</v>
       </c>
       <c r="E11">
-        <v>-32.49031547803089</v>
+        <v>-37.37927186637084</v>
       </c>
       <c r="F11">
-        <v>-2.190460721909684</v>
+        <v>-2.885559542284508</v>
       </c>
       <c r="G11">
-        <v>-18.15909658268098</v>
+        <v>-23.19986067677855</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.51336385034241</v>
       </c>
       <c r="E12">
-        <v>-32.83678223164674</v>
+        <v>-35.98273123867137</v>
       </c>
       <c r="F12">
-        <v>-2.264216281950572</v>
+        <v>-2.733926035704842</v>
       </c>
       <c r="G12">
-        <v>-17.9911608838376</v>
+        <v>-23.75057323778185</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.652097832384143</v>
       </c>
       <c r="E13">
-        <v>-33.05601018683208</v>
+        <v>-37.62151352646315</v>
       </c>
       <c r="F13">
-        <v>-2.3644403189562</v>
+        <v>-2.417210983764558</v>
       </c>
       <c r="G13">
-        <v>-17.52550285882925</v>
+        <v>-23.07771975437991</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.767964217567462</v>
       </c>
       <c r="E14">
-        <v>-32.9020511275193</v>
+        <v>-36.13155047998544</v>
       </c>
       <c r="F14">
-        <v>-2.065987771779805</v>
+        <v>-3.028739226687557</v>
       </c>
       <c r="G14">
-        <v>-17.0630395102663</v>
+        <v>-22.31358625409641</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-7.879051088352474</v>
       </c>
       <c r="E15">
-        <v>-34.22783661308592</v>
+        <v>-40.58729719509262</v>
       </c>
       <c r="F15">
-        <v>-1.913194992470038</v>
+        <v>-2.251382721064809</v>
       </c>
       <c r="G15">
-        <v>-16.50593759637221</v>
+        <v>-20.69082469692923</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.00226490803639</v>
       </c>
       <c r="E16">
-        <v>-35.90520829213406</v>
+        <v>-38.70847861405026</v>
       </c>
       <c r="F16">
-        <v>-1.760274724834078</v>
+        <v>-1.51595799696515</v>
       </c>
       <c r="G16">
-        <v>-17.270306145389</v>
+        <v>-22.5392512460536</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.162638912250937</v>
       </c>
       <c r="E17">
-        <v>-35.81327121283034</v>
+        <v>-39.4863368585848</v>
       </c>
       <c r="F17">
-        <v>-1.812149803947255</v>
+        <v>-2.137722523072593</v>
       </c>
       <c r="G17">
-        <v>-16.74422735374341</v>
+        <v>-20.6912517573038</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-5.362933148711206</v>
       </c>
       <c r="E18">
-        <v>-36.43254909032728</v>
+        <v>-39.17359365090407</v>
       </c>
       <c r="F18">
-        <v>-1.526781043191264</v>
+        <v>-2.21248215266387</v>
       </c>
       <c r="G18">
-        <v>-15.86292040464295</v>
+        <v>-20.66162071945455</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.610538580986271</v>
       </c>
       <c r="E19">
-        <v>-37.80558240945293</v>
+        <v>-40.05460826909634</v>
       </c>
       <c r="F19">
-        <v>-1.367199708474965</v>
+        <v>-1.595054605205858</v>
       </c>
       <c r="G19">
-        <v>-15.29758516399269</v>
+        <v>-22.59365344090045</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-3.914080450104743</v>
       </c>
       <c r="E20">
-        <v>-38.53094431905355</v>
+        <v>-40.60821648077105</v>
       </c>
       <c r="F20">
-        <v>-1.395791143219351</v>
+        <v>-0.937914048212287</v>
       </c>
       <c r="G20">
-        <v>-15.80705163812221</v>
+        <v>-21.53135234607695</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-3.269367494872574</v>
       </c>
       <c r="E21">
-        <v>-37.86642698621999</v>
+        <v>-43.19897231021829</v>
       </c>
       <c r="F21">
-        <v>-0.7648126160958822</v>
+        <v>-1.081644070420952</v>
       </c>
       <c r="G21">
-        <v>-16.23412359959758</v>
+        <v>-19.7198251375333</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-2.683853962670257</v>
       </c>
       <c r="E22">
-        <v>-39.00332982092668</v>
+        <v>-42.45195750214999</v>
       </c>
       <c r="F22">
-        <v>-1.03266004645641</v>
+        <v>-1.386799652884444</v>
       </c>
       <c r="G22">
-        <v>-15.15957845209709</v>
+        <v>-20.85786820374978</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.160823764857668</v>
       </c>
       <c r="E23">
-        <v>-39.23656661045474</v>
+        <v>-42.55226546565689</v>
       </c>
       <c r="F23">
-        <v>-0.7171826606890409</v>
+        <v>-0.825626923248757</v>
       </c>
       <c r="G23">
-        <v>-15.21533797061503</v>
+        <v>-20.29182119580857</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.694165826039022</v>
       </c>
       <c r="E24">
-        <v>-39.56347714906846</v>
+        <v>-41.67241466528459</v>
       </c>
       <c r="F24">
-        <v>-0.8648925358632049</v>
+        <v>-1.618838700643928</v>
       </c>
       <c r="G24">
-        <v>-16.17533989772951</v>
+        <v>-19.72333100525939</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.287556986553867</v>
       </c>
       <c r="E25">
-        <v>-38.97115727733919</v>
+        <v>-43.02818996996702</v>
       </c>
       <c r="F25">
-        <v>-0.6543356669936995</v>
+        <v>-1.40235481238589</v>
       </c>
       <c r="G25">
-        <v>-14.47420945128393</v>
+        <v>-21.69239879965311</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.9369004273010649</v>
       </c>
       <c r="E26">
-        <v>-40.15417582710299</v>
+        <v>-44.37098666814345</v>
       </c>
       <c r="F26">
-        <v>-0.5634238207708557</v>
+        <v>-2.009244380682568</v>
       </c>
       <c r="G26">
-        <v>-14.70050841271189</v>
+        <v>-19.59114257714906</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.6341627849420088</v>
       </c>
       <c r="E27">
-        <v>-38.86130102638711</v>
+        <v>-42.9017798822799</v>
       </c>
       <c r="F27">
-        <v>-0.8213263698353812</v>
+        <v>-1.328048914539387</v>
       </c>
       <c r="G27">
-        <v>-16.11703456969187</v>
+        <v>-19.11840329523221</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.3811996653429603</v>
       </c>
       <c r="E28">
-        <v>-39.63644218651705</v>
+        <v>-42.41486930002717</v>
       </c>
       <c r="F28">
-        <v>-0.6666529397510298</v>
+        <v>-1.519693167366714</v>
       </c>
       <c r="G28">
-        <v>-15.08024619406677</v>
+        <v>-20.70681794242945</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.1715975811241416</v>
       </c>
       <c r="E29">
-        <v>-40.18032776449729</v>
+        <v>-43.62550022005274</v>
       </c>
       <c r="F29">
-        <v>-0.8967954996767749</v>
+        <v>-1.828311522814315</v>
       </c>
       <c r="G29">
-        <v>-15.20780316896765</v>
+        <v>-19.50383521491463</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>0.0008778562887972515</v>
       </c>
       <c r="E30">
-        <v>-38.57491127319403</v>
+        <v>-42.79737591403306</v>
       </c>
       <c r="F30">
-        <v>-1.031134937659842</v>
+        <v>-1.34569931696696</v>
       </c>
       <c r="G30">
-        <v>-14.77249291491781</v>
+        <v>-17.48334140611387</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>0.1378153283905351</v>
       </c>
       <c r="E31">
-        <v>-39.58720408863165</v>
+        <v>-43.93947290842655</v>
       </c>
       <c r="F31">
-        <v>-0.9262825201163419</v>
+        <v>-1.58987271945054</v>
       </c>
       <c r="G31">
-        <v>-15.07875975911963</v>
+        <v>-20.08183825807091</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>0.2440870371970535</v>
       </c>
       <c r="E32">
-        <v>-39.28307403851351</v>
+        <v>-40.94322166667348</v>
       </c>
       <c r="F32">
-        <v>-1.269814464322763</v>
+        <v>-1.230221816436777</v>
       </c>
       <c r="G32">
-        <v>-14.9567545690881</v>
+        <v>-18.09107480348558</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>0.3208282875748812</v>
       </c>
       <c r="E33">
-        <v>-38.43164167677635</v>
+        <v>-42.30700331340147</v>
       </c>
       <c r="F33">
-        <v>-0.668918431063066</v>
+        <v>-2.182627712451921</v>
       </c>
       <c r="G33">
-        <v>-14.45379993803433</v>
+        <v>-20.02130493288534</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>0.3668706386907605</v>
       </c>
       <c r="E34">
-        <v>-38.65454901709291</v>
+        <v>-42.49522027858227</v>
       </c>
       <c r="F34">
-        <v>-0.5198418176838776</v>
+        <v>-1.734859412303106</v>
       </c>
       <c r="G34">
-        <v>-14.15957189268606</v>
+        <v>-18.10907589485536</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>0.3833344890820339</v>
       </c>
       <c r="E35">
-        <v>-38.27782979286882</v>
+        <v>-42.74824876376085</v>
       </c>
       <c r="F35">
-        <v>-0.6891138488967498</v>
+        <v>-1.859800347530997</v>
       </c>
       <c r="G35">
-        <v>-15.28843316084937</v>
+        <v>-17.61574005386594</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.3694909750213832</v>
       </c>
       <c r="E36">
-        <v>-38.73868353568142</v>
+        <v>-43.87747357078754</v>
       </c>
       <c r="F36">
-        <v>-0.8703974976252725</v>
+        <v>-1.613921293776488</v>
       </c>
       <c r="G36">
-        <v>-15.03262399648435</v>
+        <v>-19.70214516908082</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.3260162353551768</v>
       </c>
       <c r="E37">
-        <v>-38.45437461629486</v>
+        <v>-43.77394812649818</v>
       </c>
       <c r="F37">
-        <v>-0.9090834738746696</v>
+        <v>-2.575462005511887</v>
       </c>
       <c r="G37">
-        <v>-15.36818089234488</v>
+        <v>-19.79543303183194</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.2562085942545854</v>
       </c>
       <c r="E38">
-        <v>-37.09419084216597</v>
+        <v>-42.72638529125182</v>
       </c>
       <c r="F38">
-        <v>-1.201631965398306</v>
+        <v>-1.87308209719083</v>
       </c>
       <c r="G38">
-        <v>-16.09970717433932</v>
+        <v>-20.18947402518923</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.1618950422173683</v>
       </c>
       <c r="E39">
-        <v>-37.05942348297208</v>
+        <v>-41.44274857751159</v>
       </c>
       <c r="F39">
-        <v>-0.9143762190440682</v>
+        <v>-1.656456467253361</v>
       </c>
       <c r="G39">
-        <v>-15.56185939330163</v>
+        <v>-19.81498511378688</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.04648051158629782</v>
       </c>
       <c r="E40">
-        <v>-36.88865246390583</v>
+        <v>-42.13672136952804</v>
       </c>
       <c r="F40">
-        <v>-0.7596703229884504</v>
+        <v>-1.040691811006561</v>
       </c>
       <c r="G40">
-        <v>-15.53883123853046</v>
+        <v>-20.87592391912096</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.08624892491888346</v>
       </c>
       <c r="E41">
-        <v>-36.54754742351506</v>
+        <v>-39.64257600456044</v>
       </c>
       <c r="F41">
-        <v>-0.7280587610633212</v>
+        <v>-2.207286805408271</v>
       </c>
       <c r="G41">
-        <v>-15.93968202406203</v>
+        <v>-21.07912851486697</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.2353899370167838</v>
       </c>
       <c r="E42">
-        <v>-35.81659964122598</v>
+        <v>-37.83194718512559</v>
       </c>
       <c r="F42">
-        <v>-0.6849225711915393</v>
+        <v>-2.418933263947598</v>
       </c>
       <c r="G42">
-        <v>-15.2290171447833</v>
+        <v>-20.74597673034072</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.3989361822612502</v>
       </c>
       <c r="E43">
-        <v>-35.26234159353118</v>
+        <v>-39.1932064718313</v>
       </c>
       <c r="F43">
-        <v>-0.6579188016273813</v>
+        <v>-1.13703972778415</v>
       </c>
       <c r="G43">
-        <v>-15.72279825414776</v>
+        <v>-18.76140896173213</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.5747737367621729</v>
       </c>
       <c r="E44">
-        <v>-34.44719362978047</v>
+        <v>-38.90748014008033</v>
       </c>
       <c r="F44">
-        <v>-0.8984370108581279</v>
+        <v>-0.8903355632476974</v>
       </c>
       <c r="G44">
-        <v>-16.12085162869865</v>
+        <v>-20.01283490212311</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.7619731864294865</v>
       </c>
       <c r="E45">
-        <v>-33.78918144985892</v>
+        <v>-38.41309531147794</v>
       </c>
       <c r="F45">
-        <v>-0.8671691131166491</v>
+        <v>-1.613299689204678</v>
       </c>
       <c r="G45">
-        <v>-15.47538297799756</v>
+        <v>-20.8577854401113</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.957122282243959</v>
       </c>
       <c r="E46">
-        <v>-34.55801897417019</v>
+        <v>-38.49791815811561</v>
       </c>
       <c r="F46">
-        <v>-0.7757845306780468</v>
+        <v>-1.998141018509422</v>
       </c>
       <c r="G46">
-        <v>-15.96298329884019</v>
+        <v>-19.78476479883164</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.158200681256148</v>
       </c>
       <c r="E47">
-        <v>-33.57896289371185</v>
+        <v>-39.90834987983361</v>
       </c>
       <c r="F47">
-        <v>-1.027973068799667</v>
+        <v>-1.184089254972983</v>
       </c>
       <c r="G47">
-        <v>-15.58948258528131</v>
+        <v>-21.28769453911382</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.364544824901579</v>
       </c>
       <c r="E48">
-        <v>-34.13108123743804</v>
+        <v>-37.23280063882975</v>
       </c>
       <c r="F48">
-        <v>-0.7498711426366688</v>
+        <v>-1.551827352243939</v>
       </c>
       <c r="G48">
-        <v>-15.93584510178202</v>
+        <v>-21.86457530733229</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.57241544254233</v>
       </c>
       <c r="E49">
-        <v>-33.03586300597195</v>
+        <v>-39.25180492549055</v>
       </c>
       <c r="F49">
-        <v>-0.7465873284210051</v>
+        <v>-1.516383222003446</v>
       </c>
       <c r="G49">
-        <v>-15.08136019264073</v>
+        <v>-19.44777443675261</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.781196864118032</v>
       </c>
       <c r="E50">
-        <v>-33.04129491054415</v>
+        <v>-36.5538284169637</v>
       </c>
       <c r="F50">
-        <v>-0.8744549521806283</v>
+        <v>-1.608961126849332</v>
       </c>
       <c r="G50">
-        <v>-16.09615661424845</v>
+        <v>-19.60183398396813</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.989445087614834</v>
       </c>
       <c r="E51">
-        <v>-31.90593175700007</v>
+        <v>-36.01333466601521</v>
       </c>
       <c r="F51">
-        <v>-0.8797904574097438</v>
+        <v>-1.177740177957987</v>
       </c>
       <c r="G51">
-        <v>-16.26058644536574</v>
+        <v>-21.28624120962208</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.191750427642317</v>
       </c>
       <c r="E52">
-        <v>-30.77422761045418</v>
+        <v>-34.75471097845634</v>
       </c>
       <c r="F52">
-        <v>-0.4857161226179884</v>
+        <v>-1.087749256724971</v>
       </c>
       <c r="G52">
-        <v>-16.30758626038678</v>
+        <v>-22.37576657568777</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.387561924478301</v>
       </c>
       <c r="E53">
-        <v>-32.10682844940234</v>
+        <v>-37.03603391472247</v>
       </c>
       <c r="F53">
-        <v>-0.4738240748989536</v>
+        <v>-1.091175604473024</v>
       </c>
       <c r="G53">
-        <v>-16.60022855442173</v>
+        <v>-20.79213732206755</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.574190223868589</v>
       </c>
       <c r="E54">
-        <v>-30.94386424678151</v>
+        <v>-35.41894981013844</v>
       </c>
       <c r="F54">
-        <v>-0.4909075106087989</v>
+        <v>-1.023748533270232</v>
       </c>
       <c r="G54">
-        <v>-17.31684910512561</v>
+        <v>-19.7526640940101</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.746482195476263</v>
       </c>
       <c r="E55">
-        <v>-30.17768493671275</v>
+        <v>-37.03391232464987</v>
       </c>
       <c r="F55">
-        <v>-0.4667924206344025</v>
+        <v>-1.111858011875706</v>
       </c>
       <c r="G55">
-        <v>-17.23719075835967</v>
+        <v>-20.89199165189581</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.904358967704166</v>
       </c>
       <c r="E56">
-        <v>-29.71553831457096</v>
+        <v>-35.26898486490042</v>
       </c>
       <c r="F56">
-        <v>-0.7618645475342917</v>
+        <v>-0.9119674023466848</v>
       </c>
       <c r="G56">
-        <v>-16.38094298371872</v>
+        <v>-20.41297888618205</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.044150878756491</v>
       </c>
       <c r="E57">
-        <v>-29.96543988844725</v>
+        <v>-35.4828692207567</v>
       </c>
       <c r="F57">
-        <v>-0.233664575058054</v>
+        <v>-0.8693015731317884</v>
       </c>
       <c r="G57">
-        <v>-17.09476777871468</v>
+        <v>-22.82721242869603</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.162216338647512</v>
       </c>
       <c r="E58">
-        <v>-29.31128823261724</v>
+        <v>-33.79699533175916</v>
       </c>
       <c r="F58">
-        <v>-0.9137641167077508</v>
+        <v>-1.475183112613289</v>
       </c>
       <c r="G58">
-        <v>-16.67737916294168</v>
+        <v>-21.77472379085093</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.260569832521458</v>
       </c>
       <c r="E59">
-        <v>-28.46638366616214</v>
+        <v>-34.40542751400773</v>
       </c>
       <c r="F59">
-        <v>-0.5607259777439046</v>
+        <v>-1.594467842164188</v>
       </c>
       <c r="G59">
-        <v>-17.59902345416539</v>
+        <v>-20.69306924680486</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.337550493753596</v>
       </c>
       <c r="E60">
-        <v>-28.66454063178978</v>
+        <v>-33.4644513714799</v>
       </c>
       <c r="F60">
-        <v>-0.5841838297633938</v>
+        <v>-0.9156210118936037</v>
       </c>
       <c r="G60">
-        <v>-16.16399796871197</v>
+        <v>-22.79545602061057</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.394837841539634</v>
       </c>
       <c r="E61">
-        <v>-29.78362844975029</v>
+        <v>-31.49990877747234</v>
       </c>
       <c r="F61">
-        <v>-0.6754686387293235</v>
+        <v>-1.705429405276495</v>
       </c>
       <c r="G61">
-        <v>-17.75454129669096</v>
+        <v>-22.41402323993959</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.437927148369509</v>
       </c>
       <c r="E62">
-        <v>-28.62757469846516</v>
+        <v>-32.70062686789512</v>
       </c>
       <c r="F62">
-        <v>-0.5444304357269905</v>
+        <v>-1.535477964225899</v>
       </c>
       <c r="G62">
-        <v>-17.22309611072622</v>
+        <v>-23.05512362580161</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.466795844189784</v>
       </c>
       <c r="E63">
-        <v>-28.09243133955673</v>
+        <v>-32.04028931657064</v>
       </c>
       <c r="F63">
-        <v>-0.6774490629765806</v>
+        <v>-0.9244343353130241</v>
       </c>
       <c r="G63">
-        <v>-17.59198357907613</v>
+        <v>-23.24091806255659</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.487700102999127</v>
       </c>
       <c r="E64">
-        <v>-27.49542449722952</v>
+        <v>-32.02000401725328</v>
       </c>
       <c r="F64">
-        <v>-1.008375499949061</v>
+        <v>-1.525418264251028</v>
       </c>
       <c r="G64">
-        <v>-17.38148585150711</v>
+        <v>-24.03875622697541</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.506849839734149</v>
       </c>
       <c r="E65">
-        <v>-26.30040096287138</v>
+        <v>-33.51671901847642</v>
       </c>
       <c r="F65">
-        <v>-0.8086400935997535</v>
+        <v>-1.27507315981498</v>
       </c>
       <c r="G65">
-        <v>-17.74026953487116</v>
+        <v>-21.56907932304248</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.523569355478229</v>
       </c>
       <c r="E66">
-        <v>-26.97078719801889</v>
+        <v>-35.48055290630178</v>
       </c>
       <c r="F66">
-        <v>-0.9786461725044319</v>
+        <v>-1.928104791810943</v>
       </c>
       <c r="G66">
-        <v>-17.6190290808592</v>
+        <v>-21.46097345845758</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.545397077869745</v>
       </c>
       <c r="E67">
-        <v>-27.8893202233647</v>
+        <v>-31.91922509244958</v>
       </c>
       <c r="F67">
-        <v>-0.6323973808000746</v>
+        <v>-1.619245713064196</v>
       </c>
       <c r="G67">
-        <v>-18.05561886075998</v>
+        <v>-22.83558645363761</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.574838920131235</v>
       </c>
       <c r="E68">
-        <v>-27.44235531033363</v>
+        <v>-34.92257924568368</v>
       </c>
       <c r="F68">
-        <v>-0.9079590426747076</v>
+        <v>-2.024638794033597</v>
       </c>
       <c r="G68">
-        <v>-17.56848367156561</v>
+        <v>-21.47607451193497</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.608493328573541</v>
       </c>
       <c r="E69">
-        <v>-27.29915590526308</v>
+        <v>-32.13416684698665</v>
       </c>
       <c r="F69">
-        <v>-1.132482614012474</v>
+        <v>-1.829579279399624</v>
       </c>
       <c r="G69">
-        <v>-17.60941525661316</v>
+        <v>-20.1180903869987</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.650635414764178</v>
       </c>
       <c r="E70">
-        <v>-26.92590096365486</v>
+        <v>-34.2071029948418</v>
       </c>
       <c r="F70">
-        <v>-0.9895167299080082</v>
+        <v>-1.521641125642705</v>
       </c>
       <c r="G70">
-        <v>-17.66785962756346</v>
+        <v>-21.44104397431117</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.697901635897224</v>
       </c>
       <c r="E71">
-        <v>-27.17905171763164</v>
+        <v>-34.91776321357652</v>
       </c>
       <c r="F71">
-        <v>-1.550177922533008</v>
+        <v>-2.316843621373583</v>
       </c>
       <c r="G71">
-        <v>-16.74090191074921</v>
+        <v>-21.18738335400113</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.743837520963898</v>
       </c>
       <c r="E72">
-        <v>-27.42939028924967</v>
+        <v>-33.05101528000161</v>
       </c>
       <c r="F72">
-        <v>-1.309633582154657</v>
+        <v>-2.263344451844123</v>
       </c>
       <c r="G72">
-        <v>-16.76898692383162</v>
+        <v>-22.06553700847544</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.78848156245584</v>
       </c>
       <c r="E73">
-        <v>-27.18193182710052</v>
+        <v>-32.46445336297309</v>
       </c>
       <c r="F73">
-        <v>-1.653065752888405</v>
+        <v>-1.832972369323453</v>
       </c>
       <c r="G73">
-        <v>-17.50812249474808</v>
+        <v>-20.76004820415539</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.824360393902746</v>
       </c>
       <c r="E74">
-        <v>-27.09476323092688</v>
+        <v>-31.78578228462855</v>
       </c>
       <c r="F74">
-        <v>-1.440551423507417</v>
+        <v>-2.522890887648875</v>
       </c>
       <c r="G74">
-        <v>-17.53799851296723</v>
+        <v>-21.39330590763488</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.847308430563968</v>
       </c>
       <c r="E75">
-        <v>-27.9918720457424</v>
+        <v>-34.53273876802237</v>
       </c>
       <c r="F75">
-        <v>-1.320930156449486</v>
+        <v>-2.422313684224104</v>
       </c>
       <c r="G75">
-        <v>-17.26927491045351</v>
+        <v>-21.08744129471608</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.857721582043216</v>
       </c>
       <c r="E76">
-        <v>-26.8435099075593</v>
+        <v>-31.63339913427045</v>
       </c>
       <c r="F76">
-        <v>-1.366124372158382</v>
+        <v>-2.07940413644245</v>
       </c>
       <c r="G76">
-        <v>-16.05101236000218</v>
+        <v>-21.12705031682069</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.849617925280424</v>
       </c>
       <c r="E77">
-        <v>-28.5721597620333</v>
+        <v>-32.43011620880993</v>
       </c>
       <c r="F77">
-        <v>-2.080211826459325</v>
+        <v>-2.96048070987916</v>
       </c>
       <c r="G77">
-        <v>-16.57888877787559</v>
+        <v>-20.57122627350475</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.822816027315652</v>
       </c>
       <c r="E78">
-        <v>-27.73406149201173</v>
+        <v>-33.60841835289474</v>
       </c>
       <c r="F78">
-        <v>-2.051987019634363</v>
+        <v>-2.761632970695456</v>
       </c>
       <c r="G78">
-        <v>-15.93323308135153</v>
+        <v>-21.02497957675388</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.77763718633244</v>
       </c>
       <c r="E79">
-        <v>-27.33905628974466</v>
+        <v>-36.32498651146009</v>
       </c>
       <c r="F79">
-        <v>-2.03781285169118</v>
+        <v>-3.062632908836835</v>
       </c>
       <c r="G79">
-        <v>-16.46465840404304</v>
+        <v>-18.4776455508335</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.70856028701455</v>
       </c>
       <c r="E80">
-        <v>-29.28706089667621</v>
+        <v>-33.477500169333</v>
       </c>
       <c r="F80">
-        <v>-1.7628925907123</v>
+        <v>-2.049434877551632</v>
       </c>
       <c r="G80">
-        <v>-16.52964441297893</v>
+        <v>-19.2825881459796</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.617456861454971</v>
       </c>
       <c r="E81">
-        <v>-28.82790986009049</v>
+        <v>-34.92153543242491</v>
       </c>
       <c r="F81">
-        <v>-1.718715114201117</v>
+        <v>-2.628074299728701</v>
       </c>
       <c r="G81">
-        <v>-15.8949714512814</v>
+        <v>-19.66215543423919</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.503396824400356</v>
       </c>
       <c r="E82">
-        <v>-30.74526575493812</v>
+        <v>-34.27618033735481</v>
       </c>
       <c r="F82">
-        <v>-1.960086940920285</v>
+        <v>-2.725857054065679</v>
       </c>
       <c r="G82">
-        <v>-15.47518931108351</v>
+        <v>-18.2873388405085</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.362805078137028</v>
       </c>
       <c r="E83">
-        <v>-29.46464047641299</v>
+        <v>-36.15946172953172</v>
       </c>
       <c r="F83">
-        <v>-2.222849883439294</v>
+        <v>-2.935541300975777</v>
       </c>
       <c r="G83">
-        <v>-15.61490426447737</v>
+        <v>-19.75580580172686</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.200811526878628</v>
       </c>
       <c r="E84">
-        <v>-31.82362221343665</v>
+        <v>-34.80711674391011</v>
       </c>
       <c r="F84">
-        <v>-1.96611373378149</v>
+        <v>-2.701671489178045</v>
       </c>
       <c r="G84">
-        <v>-15.68030078106013</v>
+        <v>-16.72356623903282</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.019315716760879</v>
       </c>
       <c r="E85">
-        <v>-31.95218785475141</v>
+        <v>-37.06729397079741</v>
       </c>
       <c r="F85">
-        <v>-2.346732903115672</v>
+        <v>-2.832880732419246</v>
       </c>
       <c r="G85">
-        <v>-15.61458314156006</v>
+        <v>-18.23299623548136</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.820095514344507</v>
       </c>
       <c r="E86">
-        <v>-31.98118140958552</v>
+        <v>-39.26254193736273</v>
       </c>
       <c r="F86">
-        <v>-2.187411296169505</v>
+        <v>-1.979533265855966</v>
       </c>
       <c r="G86">
-        <v>-15.19786656653153</v>
+        <v>-16.8061279342367</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.612375401245064</v>
       </c>
       <c r="E87">
-        <v>-33.23559588055426</v>
+        <v>-38.9660310447625</v>
       </c>
       <c r="F87">
-        <v>-2.334398209593271</v>
+        <v>-3.485190986370727</v>
       </c>
       <c r="G87">
-        <v>-15.02149228710855</v>
+        <v>-17.60158416114001</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.400268306637605</v>
       </c>
       <c r="E88">
-        <v>-33.27008926707068</v>
+        <v>-37.85601149600235</v>
       </c>
       <c r="F88">
-        <v>-2.132084530013628</v>
+        <v>-3.196169407920774</v>
       </c>
       <c r="G88">
-        <v>-15.12324355953082</v>
+        <v>-15.60771375956607</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.188864790394195</v>
       </c>
       <c r="E89">
-        <v>-34.6605798534959</v>
+        <v>-40.50676734181421</v>
       </c>
       <c r="F89">
-        <v>-2.204247673756542</v>
+        <v>-3.255604307221301</v>
       </c>
       <c r="G89">
-        <v>-14.56290227682655</v>
+        <v>-16.35186149642899</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.985297488003298</v>
       </c>
       <c r="E90">
-        <v>-36.69761425941824</v>
+        <v>-41.2402555980216</v>
       </c>
       <c r="F90">
-        <v>-2.471668295372859</v>
+        <v>-3.049135775172502</v>
       </c>
       <c r="G90">
-        <v>-14.47372280108966</v>
+        <v>-18.51495705433386</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.790618828050761</v>
       </c>
       <c r="E91">
-        <v>-36.9993917672894</v>
+        <v>-41.3271570142288</v>
       </c>
       <c r="F91">
-        <v>-2.265684377334185</v>
+        <v>-3.293703520429028</v>
       </c>
       <c r="G91">
-        <v>-14.84550699678643</v>
+        <v>-17.16872867660754</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.607194197462132</v>
       </c>
       <c r="E92">
-        <v>-37.8424056958463</v>
+        <v>-41.96170264184259</v>
       </c>
       <c r="F92">
-        <v>-2.770032155017989</v>
+        <v>-3.227456310133238</v>
       </c>
       <c r="G92">
-        <v>-14.99745276067513</v>
+        <v>-17.27894170342818</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.435667140401358</v>
       </c>
       <c r="E93">
-        <v>-39.71643994409955</v>
+        <v>-44.9008271839889</v>
       </c>
       <c r="F93">
-        <v>-2.648474015625476</v>
+        <v>-3.368416430695799</v>
       </c>
       <c r="G93">
-        <v>-15.04992490747258</v>
+        <v>-17.22400982129506</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.272100341631286</v>
       </c>
       <c r="E94">
-        <v>-40.91964190251554</v>
+        <v>-44.76027240773882</v>
       </c>
       <c r="F94">
-        <v>-2.864644330112257</v>
+        <v>-3.867548272947103</v>
       </c>
       <c r="G94">
-        <v>-14.50852325579848</v>
+        <v>-17.71382655237624</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.115270378529865</v>
       </c>
       <c r="E95">
-        <v>-41.86940554885526</v>
+        <v>-45.11176803174019</v>
       </c>
       <c r="F95">
-        <v>-2.828098732407576</v>
+        <v>-3.453170828319414</v>
       </c>
       <c r="G95">
-        <v>-15.00396956956919</v>
+        <v>-19.70504520697322</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.9631430293192192</v>
       </c>
       <c r="E96">
-        <v>-43.29070334395466</v>
+        <v>-48.85542126608922</v>
       </c>
       <c r="F96">
-        <v>-2.90044241862485</v>
+        <v>-3.902617064885637</v>
       </c>
       <c r="G96">
-        <v>-14.33236250656278</v>
+        <v>-16.3398409055759</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-0.8115149762101279</v>
       </c>
       <c r="E97">
-        <v>-44.39978776283223</v>
+        <v>-48.7320792195423</v>
       </c>
       <c r="F97">
-        <v>-2.971202398926685</v>
+        <v>-4.565862016330269</v>
       </c>
       <c r="G97">
-        <v>-14.15992115524045</v>
+        <v>-16.6163227715609</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-0.6628123505007051</v>
       </c>
       <c r="E98">
-        <v>-46.7386426971288</v>
+        <v>-51.19473810473456</v>
       </c>
       <c r="F98">
-        <v>-3.464567967939874</v>
+        <v>-3.955711597553702</v>
       </c>
       <c r="G98">
-        <v>-14.12771782350719</v>
+        <v>-18.12596960874226</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-0.5159884266353979</v>
       </c>
       <c r="E99">
-        <v>-49.14368807175848</v>
+        <v>-52.90375702438531</v>
       </c>
       <c r="F99">
-        <v>-3.34446208687182</v>
+        <v>-3.543766725212128</v>
       </c>
       <c r="G99">
-        <v>-14.80571589467716</v>
+        <v>-17.09167903972654</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.3763309495186593</v>
       </c>
       <c r="E100">
-        <v>-50.42709156908732</v>
+        <v>-54.45267853820589</v>
       </c>
       <c r="F100">
-        <v>-3.593388190807634</v>
+        <v>-4.267188542178671</v>
       </c>
       <c r="G100">
-        <v>-15.16832325813907</v>
+        <v>-18.58370880882067</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.2447355592180587</v>
       </c>
       <c r="E101">
-        <v>-51.54266189486238</v>
+        <v>-54.73792371959353</v>
       </c>
       <c r="F101">
-        <v>-3.508189563674738</v>
+        <v>-4.511863979437446</v>
       </c>
       <c r="G101">
-        <v>-14.67003649629567</v>
+        <v>-16.84007426819639</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.1346324041822431</v>
       </c>
       <c r="E102">
-        <v>-52.97633261306924</v>
+        <v>-54.65411638325208</v>
       </c>
       <c r="F102">
-        <v>-3.494416073328162</v>
+        <v>-4.588008559851774</v>
       </c>
       <c r="G102">
-        <v>-15.04276419747114</v>
+        <v>-17.49323828200352</v>
       </c>
     </row>
   </sheetData>
